--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488284_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488284_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.3187</v>
+        <v>13.0473</v>
       </c>
       <c r="E2" t="n">
-        <v>9.6928</v>
+        <v>9.790699999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>3.626</v>
+        <v>3.2567</v>
       </c>
       <c r="G2" t="n">
         <v>9.6615</v>
@@ -610,13 +610,13 @@
         <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0458</v>
+        <v>0.7744</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2574</v>
+        <v>0.3554</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7884</v>
+        <v>0.419</v>
       </c>
       <c r="V2" t="n">
         <v>0.9439</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>10.5762</v>
+        <v>10.9958</v>
       </c>
       <c r="E3" t="n">
-        <v>7.8796</v>
+        <v>8.7178</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6966</v>
+        <v>2.278</v>
       </c>
       <c r="G3" t="n">
         <v>11.3339</v>
@@ -688,13 +688,13 @@
         <v>2.2234</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1833</v>
+        <v>0.2363</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6143</v>
+        <v>0.2239</v>
       </c>
       <c r="U3" t="n">
-        <v>0.431</v>
+        <v>0.0124</v>
       </c>
       <c r="V3" t="n">
         <v>-0.945</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1156</v>
+        <v>5.76</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6223</v>
+        <v>4.2421</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4933</v>
+        <v>1.5179</v>
       </c>
       <c r="G4" t="n">
         <v>2.3363</v>
@@ -766,13 +766,13 @@
         <v>0.7411</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1493</v>
+        <v>0.7937</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1291</v>
+        <v>0.7489</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0201</v>
+        <v>0.0448</v>
       </c>
       <c r="V4" t="n">
         <v>1.8888</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.9774</v>
+        <v>5.4161</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3677</v>
+        <v>4.4863</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6097</v>
+        <v>0.9298</v>
       </c>
       <c r="G5" t="n">
         <v>3.639</v>
@@ -844,13 +844,13 @@
         <v>1.8529</v>
       </c>
       <c r="S5" t="n">
-        <v>1.115</v>
+        <v>0.5537</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5631</v>
+        <v>0.6818</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4482</v>
+        <v>-0.1281</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6294</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7178</v>
+        <v>3.0625</v>
       </c>
       <c r="E6" t="n">
         <v>1.9837</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7341</v>
+        <v>1.0788</v>
       </c>
       <c r="G6" t="n">
         <v>4.1515</v>
@@ -922,13 +922,13 @@
         <v>1.4823</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4691</v>
+        <v>-0.1244</v>
       </c>
       <c r="T6" t="n">
         <v>0.1816</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6506</v>
+        <v>-0.3059</v>
       </c>
       <c r="V6" t="n">
         <v>1.2589</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1505</v>
+        <v>2.3278</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8215</v>
+        <v>0.9741</v>
       </c>
       <c r="F7" t="n">
-        <v>1.329</v>
+        <v>1.3537</v>
       </c>
       <c r="G7" t="n">
         <v>0.3241</v>
@@ -1000,13 +1000,13 @@
         <v>1.8529</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0259</v>
+        <v>0.1514</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0174</v>
+        <v>0.1701</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0433</v>
+        <v>-0.0187</v>
       </c>
       <c r="V7" t="n">
         <v>-0.0005</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. CABALLERO CARPIO</t>
+          <t>F. GONZÁLEZ ROSCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3383</v>
+        <v>1.2441</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6599</v>
+        <v>1.2441</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6784</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2049</v>
+        <v>1.2441</v>
       </c>
       <c r="H8" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2119</v>
+        <v>1.2441</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3689</v>
+        <v>1.2441</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1201</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2488</v>
+        <v>1.2441</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5738</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1131</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4607</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6168</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.291</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3258</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. GONZÁLEZ ROSCO</t>
+          <t>S. CABALLERO CARPIO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2441</v>
+        <v>1.2267</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2441</v>
+        <v>0.6714</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.5553</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2441</v>
+        <v>-0.2049</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2441</v>
+        <v>-0.2119</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2441</v>
+        <v>0.3689</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.1201</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2441</v>
+        <v>0.2488</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-0.5738</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.1131</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.4607</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.5052</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.3025</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.2027</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9895</v>
+        <v>0.6344</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7617</v>
+        <v>0.2835</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2278</v>
+        <v>0.3509</v>
       </c>
       <c r="G10" t="n">
         <v>0.6022</v>
@@ -1234,13 +1234,13 @@
         <v>0.9264</v>
       </c>
       <c r="S10" t="n">
-        <v>0.09080000000000001</v>
+        <v>-0.2643</v>
       </c>
       <c r="T10" t="n">
-        <v>0.868</v>
+        <v>0.3899</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7772</v>
+        <v>-0.6541</v>
       </c>
       <c r="V10" t="n">
         <v>-0.63</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. LÓPEZ CALZADA</t>
+          <t>A. USAOLA REDONDO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3221</v>
+        <v>0.4137</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3221</v>
+        <v>1.5153</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-1.1016</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3221</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3221</v>
+        <v>0.5827</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.2747</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3221</v>
+        <v>1.8836</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3221</v>
+        <v>0.4724</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.4113</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>-1.0263</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>0.1103</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-1.1366</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0.2033</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>0.2257</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0.429</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.9433</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. USAOLA REDONDO</t>
+          <t>L. LÓPEZ CALZADA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3134</v>
+        <v>0.3221</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.3221</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.077</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.3221</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5827</v>
+        <v>0.3221</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2747</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.8836</v>
+        <v>0.3221</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4724</v>
+        <v>0.3221</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4113</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0263</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1103</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1366</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.297</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9304</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.526</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4044</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.9433</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.7533</v>
+        <v>-1.1045</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.7843</v>
+        <v>-0.2831</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9691</v>
+        <v>-0.8213</v>
       </c>
       <c r="G14" t="n">
         <v>-0.0785</v>
@@ -1546,13 +1546,13 @@
         <v>0.7411</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5457</v>
+        <v>0.1032</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3071</v>
+        <v>0.194</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2385</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9439</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.3063</v>
+        <v>-2.1482</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.6362</v>
+        <v>-2.4288</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3299</v>
+        <v>0.2807</v>
       </c>
       <c r="G15" t="n">
         <v>-1.4523</v>
@@ -1624,13 +1624,13 @@
         <v>1.1117</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2196</v>
+        <v>0.3777</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3669</v>
+        <v>0.5742</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1473</v>
+        <v>-0.1965</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2589</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>40.99929999999999</v>
+        <v>41.8199</v>
       </c>
       <c r="E16" t="n">
-        <v>31.3206</v>
+        <v>32.1413</v>
       </c>
       <c r="F16" t="n">
-        <v>9.678700000000001</v>
+        <v>9.678899999999999</v>
       </c>
       <c r="G16" t="n">
         <v>33.35850000000001</v>
@@ -1702,10 +1702,10 @@
         <v>14.8228</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0829</v>
+        <v>2.9036</v>
       </c>
       <c r="T16" t="n">
-        <v>3.227099999999999</v>
+        <v>4.048</v>
       </c>
       <c r="U16" t="n">
         <v>-1.1442</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. NDIAYE</t>
+          <t>F. VALDIVIA SANTILLANA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9089</v>
+        <v>-2.2663</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3622</v>
+        <v>0.3555</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2711</v>
+        <v>-2.6219</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.9256</v>
+        <v>-2.6486</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.8291</v>
+        <v>-2.2093</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0965</v>
+        <v>-0.4393</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6322</v>
+        <v>1.8696</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.4829</v>
+        <v>-0.8166</v>
       </c>
       <c r="L17" t="n">
-        <v>2.115</v>
+        <v>2.6862</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.5578</v>
+        <v>-4.5182</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3463</v>
+        <v>-1.3927</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.2115</v>
+        <v>-3.1255</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7411</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R17" t="n">
         <v>1.6676</v>
       </c>
       <c r="S17" t="n">
-        <v>2.2195</v>
+        <v>-0.0619</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6564</v>
+        <v>-0.2906</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.2288</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9439</v>
+        <v>0.6294</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. QUINTA RAMOS</t>
+          <t>F. NDIAYE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.0848</v>
+        <v>-2.3576</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5226</v>
+        <v>0.285</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.6074</v>
+        <v>-2.6426</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.9417</v>
+        <v>-2.9256</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6778</v>
+        <v>-2.8291</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.2639</v>
+        <v>-0.0965</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3912</v>
+        <v>0.6322</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4896</v>
+        <v>-1.4829</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.0984</v>
+        <v>2.115</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.3329</v>
+        <v>-3.5578</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.1674</v>
+        <v>-1.3463</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.1656</v>
+        <v>-2.2115</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.4087</v>
+        <v>0.7411</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.7057</v>
+        <v>-0.9264</v>
       </c>
       <c r="R18" t="n">
-        <v>1.297</v>
+        <v>1.6676</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3144</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>1.69</v>
+        <v>0.5792</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3756</v>
+        <v>0.1915</v>
       </c>
       <c r="V18" t="n">
-        <v>1.9513</v>
+        <v>-0.9439</v>
       </c>
       <c r="W18" t="n">
-        <v>3.1471</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1959</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. VALDIVIA SANTILLANA</t>
+          <t>D. RODRIGUEZ GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.3928</v>
+        <v>-3.6256</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.33</v>
+        <v>-1.1425</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.0628</v>
+        <v>-2.4831</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.6486</v>
+        <v>-3.8914</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.2093</v>
+        <v>-1.5477</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4393</v>
+        <v>-2.3438</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8696</v>
+        <v>-0.484</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8166</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>2.6862</v>
+        <v>0.0829</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.5182</v>
+        <v>-3.4074</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3927</v>
+        <v>-0.9807</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.1255</v>
+        <v>-2.4267</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1853</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6676</v>
+        <v>0.3706</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1883</v>
+        <v>0.1287</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9762</v>
+        <v>0.268</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2122</v>
+        <v>-0.1393</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6294</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.6929999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. RODRIGUEZ GARCIA</t>
+          <t>J. CARO SERRANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.149</v>
+        <v>-4.0503</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3383</v>
+        <v>-1.5526</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8107</v>
+        <v>-2.4977</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.8914</v>
+        <v>-4.6206</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5477</v>
+        <v>-1.3904</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.3438</v>
+        <v>-3.2302</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.484</v>
+        <v>-1.7668</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5669999999999999</v>
+        <v>0.1503</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0829</v>
+        <v>-1.9171</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.4074</v>
+        <v>-2.8538</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9807</v>
+        <v>-1.5407</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.4267</v>
+        <v>-1.3131</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.3706</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0.3706</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3947</v>
+        <v>-0.1788</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0721</v>
+        <v>0.2142</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4668</v>
+        <v>-0.393</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.3785</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.3785</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. PENAS REINO</t>
+          <t>J. QUINTA RAMOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4973</v>
+        <v>-4.1946</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9394</v>
+        <v>0.1516</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.5579</v>
+        <v>-4.3462</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.9144</v>
+        <v>-3.9417</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7642</v>
+        <v>-0.6778</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.1502</v>
+        <v>-3.2639</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0546</v>
+        <v>0.3912</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5153</v>
+        <v>1.4896</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5699</v>
+        <v>-1.0984</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.8598</v>
+        <v>-4.3329</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2796</v>
+        <v>-2.1674</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.5803</v>
+        <v>-2.1656</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8529</v>
+        <v>-2.4087</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.7793</v>
+        <v>-3.7057</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9264</v>
+        <v>1.297</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2636</v>
+        <v>0.2046</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6367</v>
+        <v>0.319</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3731</v>
+        <v>-0.1144</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0063</v>
+        <v>1.9513</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2578</v>
+        <v>3.1471</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2514</v>
+        <v>-1.1959</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CARO SERRANO</t>
+          <t>D. PENAS REINO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8589</v>
+        <v>-4.4395</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2381</v>
+        <v>-1.1353</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6208</v>
+        <v>-3.3042</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.6206</v>
+        <v>-3.9144</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3904</v>
+        <v>-0.7642</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.2302</v>
+        <v>-3.1502</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.7668</v>
+        <v>-0.0546</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1503</v>
+        <v>0.5153</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.9171</v>
+        <v>-0.5699</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.8538</v>
+        <v>-3.8598</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5407</v>
+        <v>-1.2796</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3131</v>
+        <v>-2.5803</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3706</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3706</v>
+        <v>0.9264</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9874000000000001</v>
+        <v>0.3215</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4713</v>
+        <v>0.4409</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5161</v>
+        <v>-0.1194</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3785</v>
+        <v>1.0063</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2578</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3785</v>
+        <v>-0.2514</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7085</v>
+        <v>-4.8346</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9612</v>
+        <v>-1.4716</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.7473</v>
+        <v>-3.3631</v>
       </c>
       <c r="G23" t="n">
         <v>-4.5792</v>
@@ -2248,13 +2248,13 @@
         <v>0.9264</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8044</v>
+        <v>-0.9305</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9637</v>
+        <v>-0.4741</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8406</v>
+        <v>-0.4564</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2514</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>H. HERNANDEZ CASTANO</t>
+          <t>M. MALICK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.8375</v>
+        <v>-6.189</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8995</v>
+        <v>-2.1715</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.938</v>
+        <v>-4.0175</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.0149</v>
+        <v>-2.822</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.0949</v>
+        <v>-1.9371</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.92</v>
+        <v>-0.8849</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.5041</v>
+        <v>2.1951</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.1984</v>
+        <v>-0.4603</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3057</v>
+        <v>2.6554</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5108</v>
+        <v>-5.0171</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8966</v>
+        <v>-1.4768</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6143</v>
+        <v>-3.5403</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9264</v>
+        <v>-3.7057</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3706</v>
+        <v>1.6676</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2509</v>
+        <v>-0.3839</v>
       </c>
       <c r="T24" t="n">
-        <v>0.531</v>
+        <v>-0.3454</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2801</v>
+        <v>-0.0386</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.5177</v>
+        <v>-0.945</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.5177</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. MALICK</t>
+          <t>H. HERNANDEZ CASTANO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.5617</v>
+        <v>-7.0832</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.857</v>
+        <v>-2.9974</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.7047</v>
+        <v>-4.0858</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.822</v>
+        <v>-4.0149</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.9371</v>
+        <v>-2.0949</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8849</v>
+        <v>-1.92</v>
       </c>
       <c r="J25" t="n">
-        <v>2.1951</v>
+        <v>-2.5041</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.4603</v>
+        <v>-1.1984</v>
       </c>
       <c r="L25" t="n">
-        <v>2.6554</v>
+        <v>-1.3057</v>
       </c>
       <c r="M25" t="n">
-        <v>-5.0171</v>
+        <v>-1.5108</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.4768</v>
+        <v>-0.8966</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.5403</v>
+        <v>-0.6143</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.0382</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.7057</v>
+        <v>-0.9264</v>
       </c>
       <c r="R25" t="n">
-        <v>1.6676</v>
+        <v>0.3706</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.7566</v>
+        <v>0.0053</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0309</v>
+        <v>0.4331</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7257</v>
+        <v>-0.4278</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.945</v>
+        <v>-2.5177</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.3155</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.6294</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-40.9994</v>
+        <v>-39.0407</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.678699999999999</v>
+        <v>-9.678799999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-31.3207</v>
+        <v>-29.3621</v>
       </c>
       <c r="G26" t="n">
         <v>-33.3584</v>
@@ -2455,13 +2455,13 @@
         <v>-17.3564</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.7189000000000005</v>
+        <v>-0.7189000000000003</v>
       </c>
       <c r="K26" t="n">
         <v>-3.4825</v>
       </c>
       <c r="L26" t="n">
-        <v>2.7634</v>
+        <v>2.763400000000001</v>
       </c>
       <c r="M26" t="n">
         <v>-32.63950000000001</v>
@@ -2479,19 +2479,19 @@
         <v>-14.8228</v>
       </c>
       <c r="R26" t="n">
-        <v>9.2644</v>
+        <v>9.264399999999998</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.083</v>
+        <v>-0.1242999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>1.1441</v>
+        <v>1.1443</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.2272</v>
+        <v>-1.2686</v>
       </c>
       <c r="V26" t="n">
-        <v>0.000500000000000278</v>
+        <v>0.000500000000000167</v>
       </c>
       <c r="W26" t="n">
         <v>4.7188</v>
